--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -1,45 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Xola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E0DC27-17EB-4E91-BFC4-A2089FFD7F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84914788-2647-4480-8A7C-6E793EB1AC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21960" yWindow="615" windowWidth="6885" windowHeight="14865" activeTab="2" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="17736" yWindow="0" windowWidth="5400" windowHeight="13776" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="T3" sheetId="1" r:id="rId1"/>
     <sheet name="T4" sheetId="2" r:id="rId2"/>
     <sheet name="T5" sheetId="3" r:id="rId3"/>
+    <sheet name="T6" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="6">
   <si>
     <t>Tầng</t>
   </si>
@@ -67,7 +56,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -487,9 +476,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CB08FB-80B1-4D9C-AAE4-0416F8953E35}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -502,7 +491,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -513,7 +502,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -524,7 +513,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -535,7 +524,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -546,7 +535,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -557,7 +546,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -568,7 +557,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -579,7 +568,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -590,7 +579,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -601,7 +590,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -612,7 +601,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -625,7 +614,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -637,7 +626,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -646,7 +635,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -655,7 +644,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -664,7 +653,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -673,7 +662,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -682,7 +671,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -691,7 +680,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -700,7 +689,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -709,7 +698,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -718,7 +707,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -727,7 +716,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -736,7 +725,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -745,7 +734,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -754,7 +743,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -763,7 +752,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -772,7 +761,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -781,7 +770,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -790,7 +779,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -799,7 +788,7 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>4</v>
       </c>
@@ -816,7 +805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="1">
         <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
@@ -848,9 +837,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064059B2-0CFC-4C91-B4E1-43670BB0799C}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -863,7 +852,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -874,7 +863,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -885,7 +874,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -896,7 +885,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -907,7 +896,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -918,7 +907,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -929,7 +918,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -940,7 +929,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -951,7 +940,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -962,7 +951,7 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -973,7 +962,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -984,7 +973,7 @@
       <c r="D12" s="4"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -998,7 +987,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1009,7 +998,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1020,7 +1009,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1031,7 +1020,7 @@
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1042,7 +1031,7 @@
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1053,7 +1042,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1064,7 +1053,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1075,7 +1064,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1086,7 +1075,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1097,7 +1086,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1108,7 +1097,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1119,7 +1108,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1130,7 +1119,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1141,7 +1130,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1152,7 +1141,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1163,7 +1152,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1174,7 +1163,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1185,7 +1174,7 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1196,7 +1185,7 @@
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1207,7 +1196,7 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1218,7 +1207,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1229,7 +1218,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1240,7 +1229,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1251,7 +1240,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1262,7 +1251,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1273,7 +1262,7 @@
       <c r="D38" s="3"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1284,7 +1273,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1295,7 +1284,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1306,7 +1295,7 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
@@ -1323,7 +1312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="B43" s="1">
         <f>COUNTIF(B2:B41, "Up")</f>
@@ -1355,9 +1344,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E34279-DF0B-49D0-978E-1339C67697A9}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1370,7 +1359,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1381,7 +1370,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1392,7 +1381,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1403,7 +1392,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1414,7 +1403,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1425,7 +1414,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1436,7 +1425,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1447,7 +1436,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1458,7 +1447,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1469,7 +1458,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1480,7 +1469,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1491,7 +1480,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1505,7 +1494,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1516,7 +1505,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1527,7 +1516,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1538,7 +1527,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1549,7 +1538,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1560,7 +1549,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1571,7 +1560,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1582,7 +1571,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1593,7 +1582,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1604,7 +1593,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1615,7 +1604,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1624,7 +1613,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1633,7 +1622,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1642,7 +1631,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1651,7 +1640,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1660,7 +1649,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1669,7 +1658,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1678,7 +1667,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1687,7 +1676,7 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1696,7 +1685,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1705,7 +1694,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1714,7 +1703,7 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1723,7 +1712,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1732,7 +1721,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1741,7 +1730,7 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1750,7 +1739,7 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1759,7 +1748,7 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1768,7 +1757,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1777,7 +1766,7 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
@@ -1794,7 +1783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="11"/>
       <c r="B43" s="1">
         <f>COUNTIF(B2:B41, "Up")</f>
@@ -1811,6 +1800,491 @@
       <c r="E43" s="1">
         <f>COUNTIF(B2:B41, "Right")</f>
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A42:A43"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66B4146-75A4-41C4-A73E-146E823D5C6D}">
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="11"/>
+      <c r="B43" s="1">
+        <f>COUNTIF(B2:B41, "Up")</f>
+        <v>7</v>
+      </c>
+      <c r="C43" s="1">
+        <f>COUNTIF(B2:B41, "Dow")</f>
+        <v>7</v>
+      </c>
+      <c r="D43" s="1">
+        <f>COUNTIF(B2:B41, "Left")</f>
+        <v>8</v>
+      </c>
+      <c r="E43" s="1">
+        <f>COUNTIF(B2:B41, "Right")</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -5,20 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\Xola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\hiep\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84914788-2647-4480-8A7C-6E793EB1AC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BBD48B-E9E4-4D83-8114-4ED3423DE12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17736" yWindow="0" windowWidth="5400" windowHeight="13776" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="16968" yWindow="0" windowWidth="6108" windowHeight="13776" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="T3" sheetId="1" r:id="rId1"/>
     <sheet name="T4" sheetId="2" r:id="rId2"/>
     <sheet name="T5" sheetId="3" r:id="rId3"/>
     <sheet name="T6" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="13">
   <si>
     <t>Tầng</t>
   </si>
@@ -46,6 +47,27 @@
   </si>
   <si>
     <t>Dow</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>lên</t>
+  </si>
+  <si>
+    <t>xuống</t>
+  </si>
+  <si>
+    <t>trái</t>
+  </si>
+  <si>
+    <t>phải</t>
+  </si>
+  <si>
+    <t>sai</t>
+  </si>
+  <si>
+    <t>đúng</t>
   </si>
 </sst>
 </file>
@@ -140,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -161,6 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1814,485 +1837,662 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66B4146-75A4-41C4-A73E-146E823D5C6D}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="1"/>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="1"/>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="1"/>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="1"/>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="1"/>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1"/>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="B32" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="B34" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="1">
-        <f>COUNTIF(B2:B41, "Up")</f>
-        <v>7</v>
-      </c>
-      <c r="C43" s="1">
-        <f>COUNTIF(B2:B41, "Dow")</f>
-        <v>7</v>
-      </c>
-      <c r="D43" s="1">
-        <f>COUNTIF(B2:B41, "Left")</f>
-        <v>8</v>
-      </c>
-      <c r="E43" s="1">
-        <f>COUNTIF(B2:B41, "Right")</f>
-        <v>5</v>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A42:A43"/>
-  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72485C5-B1AA-46B0-AF62-B61CED32615E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\hiep\Xola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BBD48B-E9E4-4D83-8114-4ED3423DE12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16A34D3-9D3B-472D-9F79-33BA612B3929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16968" yWindow="0" windowWidth="6108" windowHeight="13776" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="T3" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,29 @@
     <sheet name="T6" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="13">
   <si>
     <t>Tầng</t>
   </si>
@@ -78,7 +90,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -183,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,9 +511,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CB08FB-80B1-4D9C-AAE4-0416F8953E35}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -514,7 +526,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -525,7 +537,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -536,7 +548,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -547,7 +559,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -558,7 +570,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -569,7 +581,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -580,7 +592,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -591,7 +603,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -602,7 +614,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -613,7 +625,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -624,7 +636,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -637,7 +649,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -649,7 +661,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -658,7 +670,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -667,7 +679,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -676,7 +688,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -685,7 +697,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -694,7 +706,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -703,7 +715,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -712,7 +724,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -721,7 +733,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -730,7 +742,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -739,7 +751,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -748,7 +760,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -757,7 +769,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -766,7 +778,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -775,7 +787,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -784,7 +796,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -793,7 +805,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -802,7 +814,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -811,7 +823,7 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>4</v>
       </c>
@@ -828,7 +840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="1">
         <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
@@ -860,9 +872,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064059B2-0CFC-4C91-B4E1-43670BB0799C}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -875,7 +887,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -886,7 +898,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -897,7 +909,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -908,7 +920,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -919,7 +931,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -930,7 +942,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -941,7 +953,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -952,7 +964,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -963,7 +975,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -974,7 +986,7 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -985,7 +997,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -996,7 +1008,7 @@
       <c r="D12" s="4"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1010,7 +1022,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1021,7 +1033,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1032,7 +1044,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1043,7 +1055,7 @@
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1054,7 +1066,7 @@
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1065,7 +1077,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1076,7 +1088,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1087,7 +1099,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1098,7 +1110,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1109,7 +1121,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1120,7 +1132,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1131,7 +1143,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1142,7 +1154,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1153,7 +1165,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1164,7 +1176,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1175,7 +1187,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1186,7 +1198,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1197,7 +1209,7 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1208,7 +1220,7 @@
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1219,7 +1231,7 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1230,7 +1242,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1241,7 +1253,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1252,7 +1264,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1263,7 +1275,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1274,7 +1286,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1285,7 +1297,7 @@
       <c r="D38" s="3"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1296,7 +1308,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1307,7 +1319,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1318,7 +1330,7 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
@@ -1335,7 +1347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
       <c r="B43" s="1">
         <f>COUNTIF(B2:B41, "Up")</f>
@@ -1367,9 +1379,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E34279-DF0B-49D0-978E-1339C67697A9}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1394,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1393,7 +1405,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1404,7 +1416,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1415,7 +1427,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1426,7 +1438,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1437,7 +1449,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1448,7 +1460,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1459,7 +1471,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1470,7 +1482,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1481,7 +1493,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1492,7 +1504,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1503,7 +1515,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1517,7 +1529,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1528,7 +1540,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1539,7 +1551,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1550,7 +1562,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1561,7 +1573,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1572,7 +1584,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1583,7 +1595,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1594,7 +1606,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1605,7 +1617,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1616,7 +1628,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1627,7 +1639,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1636,7 +1648,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1645,7 +1657,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1654,7 +1666,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1663,7 +1675,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1672,7 +1684,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1681,7 +1693,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1690,7 +1702,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1699,7 +1711,7 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1708,7 +1720,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1717,7 +1729,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1726,7 +1738,7 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1735,7 +1747,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1744,7 +1756,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1753,7 +1765,7 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1762,7 +1774,7 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1771,7 +1783,7 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1780,7 +1792,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1789,7 +1801,7 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
       <c r="B43" s="1">
         <f>COUNTIF(B2:B41, "Up")</f>
@@ -1838,15 +1850,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66B4146-75A4-41C4-A73E-146E823D5C6D}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1863,7 +1874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1880,7 +1891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1897,7 +1908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1914,7 +1925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1931,7 +1942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1948,7 +1959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1965,7 +1976,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1982,7 +1993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1999,7 +2010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2016,7 +2027,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2033,7 +2044,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2050,7 +2061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2067,7 +2078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2084,7 +2095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2101,7 +2112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2118,7 +2129,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2135,7 +2146,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2152,7 +2163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2169,7 +2180,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2186,7 +2197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2203,7 +2214,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2220,7 +2231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2237,7 +2248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2254,7 +2265,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2271,7 +2282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2288,7 +2299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2305,7 +2316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2322,7 +2333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2333,7 +2344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2344,154 +2355,105 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="B33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="B34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="B35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="B36" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="B37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="B39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="B40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="12"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>12</v>
+      <c r="B41" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72485C5-B1AA-46B0-AF62-B61CED32615E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Dianguc.xlsx
+++ b/Dianguc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tool\Xola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\.tool\hiep\Xola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16A34D3-9D3B-472D-9F79-33BA612B3929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9B21AB-16AD-43FF-A441-B6295137C680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
+    <workbookView xWindow="18984" yWindow="0" windowWidth="4152" windowHeight="13776" activeTab="3" xr2:uid="{210B81C1-063E-40AF-8D8C-307F53B87FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="T3" sheetId="1" r:id="rId1"/>
@@ -19,22 +19,10 @@
     <sheet name="T6" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -76,21 +64,28 @@
     <t>phải</t>
   </si>
   <si>
-    <t>sai</t>
+    <t>đúng</t>
   </si>
   <si>
-    <t>đúng</t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -183,6 +178,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -195,7 +191,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,22 +508,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CB08FB-80B1-4D9C-AAE4-0416F8953E35}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="b">
+      <c r="C1" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -537,7 +534,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -548,7 +545,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -559,7 +556,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -570,7 +567,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -581,7 +578,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -592,7 +589,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -603,7 +600,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -614,7 +611,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -625,7 +622,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -636,7 +633,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -649,7 +646,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -657,11 +654,11 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -670,7 +667,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -679,7 +676,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -688,7 +685,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -697,7 +694,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -706,7 +703,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -715,7 +712,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -724,7 +721,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -733,7 +730,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -742,7 +739,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -751,7 +748,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -760,7 +757,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -769,7 +766,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -778,7 +775,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -787,7 +784,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -796,7 +793,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -805,7 +802,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -814,7 +811,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -823,8 +820,8 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -840,8 +837,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
       <c r="B33" s="1">
         <f>COUNTIF(B2:B31, "Up") / COUNTA(A2:A31)</f>
         <v>6.6666666666666666E-2</v>
@@ -872,22 +869,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064059B2-0CFC-4C91-B4E1-43670BB0799C}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="b">
+      <c r="C1" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -898,7 +895,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -909,7 +906,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -920,7 +917,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -931,7 +928,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -942,7 +939,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -953,7 +950,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -964,7 +961,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -975,7 +972,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -986,7 +983,7 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -997,7 +994,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1008,7 +1005,7 @@
       <c r="D12" s="4"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1018,11 +1015,11 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1033,7 +1030,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1044,7 +1041,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1055,7 +1052,7 @@
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1066,7 +1063,7 @@
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1077,7 +1074,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1088,7 +1085,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1099,7 +1096,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1110,7 +1107,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1121,7 +1118,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1132,7 +1129,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1143,7 +1140,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1154,7 +1151,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1165,7 +1162,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1176,7 +1173,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1187,7 +1184,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1198,7 +1195,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1209,7 +1206,7 @@
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1220,7 +1217,7 @@
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1231,7 +1228,7 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1242,7 +1239,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1253,7 +1250,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1264,7 +1261,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1275,7 +1272,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1286,7 +1283,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1297,7 +1294,7 @@
       <c r="D38" s="3"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1308,7 +1305,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1319,7 +1316,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1330,8 +1327,8 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -1347,8 +1344,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12"/>
       <c r="B43" s="1">
         <f>COUNTIF(B2:B41, "Up")</f>
         <v>6</v>
@@ -1379,22 +1376,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E34279-DF0B-49D0-978E-1339C67697A9}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="b">
+      <c r="C1" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1405,7 +1402,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1416,7 +1413,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1427,7 +1424,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1438,7 +1435,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1449,7 +1446,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1460,7 +1457,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1471,7 +1468,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1482,7 +1479,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1493,7 +1490,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1504,7 +1501,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1515,7 +1512,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1525,11 +1522,11 @@
       <c r="C13" s="7"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1540,7 +1537,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1551,7 +1548,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1562,7 +1559,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1573,7 +1570,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1584,7 +1581,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1595,7 +1592,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1606,7 +1603,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1617,7 +1614,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1628,7 +1625,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1639,7 +1636,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1648,7 +1645,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1657,7 +1654,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1666,7 +1663,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1675,7 +1672,7 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1684,7 +1681,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1693,7 +1690,7 @@
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1702,7 +1699,7 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1711,7 +1708,7 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1720,7 +1717,7 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1729,7 +1726,7 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1738,7 +1735,7 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1747,7 +1744,7 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1756,7 +1753,7 @@
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1765,7 +1762,7 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1774,7 +1771,7 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1783,7 +1780,7 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1792,7 +1789,7 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1801,8 +1798,8 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B42" s="7" t="s">
@@ -1818,8 +1815,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12"/>
       <c r="B43" s="1">
         <f>COUNTIF(B2:B41, "Up")</f>
         <v>6</v>
@@ -1850,15 +1847,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66B4146-75A4-41C4-A73E-146E823D5C6D}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B1" t="s">
@@ -1874,570 +1871,570 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="14">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="14">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="14">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="14">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="14">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="14">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="14">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="12"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
+      <c r="C40" s="8"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="14">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -2453,7 +2450,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72485C5-B1AA-46B0-AF62-B61CED32615E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
